--- a/DateBase/orders/Dang Nguyen48_2026-3-11.xlsx
+++ b/DateBase/orders/Dang Nguyen48_2026-3-11.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L11"/>
+  <dimension ref="A1:L21"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -524,12 +524,93 @@
         <v>816_山里红_undefined_undefined_1bunch</v>
       </c>
       <c r="F11" t="str">
-        <v>1</v>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="C12" t="str">
+        <v>344_钢草_steal grass_Xanthorrhoea preissii Endl._1bunch</v>
+      </c>
+      <c r="F12" t="str">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="C13" t="str">
+        <v>106_绣球粉_Hydrangea Pink S_Hydrangea L._1stem</v>
+      </c>
+      <c r="F13" t="str">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="C14" t="str">
+        <v>107_绣球浅粉_Hydrangea Light Pink S_Hydrangea L._1stem</v>
+      </c>
+      <c r="F14" t="str">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="C15" t="str">
+        <v>326_红继木_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F15" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="C16" t="str">
+        <v>325_小盼草_Northern Sea Oats_undefined_1bunch</v>
+      </c>
+      <c r="F16" t="str">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="17" xml:space="preserve">
+      <c r="C17" t="str" xml:space="preserve">
+        <v xml:space="preserve">510_翠珠白_Didiscus caeruleus 
+white_Trachymene Coerulea_1bunch</v>
+      </c>
+      <c r="F17" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="C18" t="str">
+        <v>577_腊梅白_wax white_undefined_1bunch</v>
+      </c>
+      <c r="F18" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="C19" t="str">
+        <v>578_腊梅粉_wax pink_undefined_1bunch</v>
+      </c>
+      <c r="F19" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>3</v>
+      </c>
+      <c r="C20" t="str">
+        <v>533_风车果_scabiosa pods_undefined_1bunch</v>
+      </c>
+      <c r="F20" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="C21" t="str">
+        <v>791_菟葵黑_undefined_undefined_1bunch</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L11"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L21"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -584,7 +665,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>01010810108810101</v>
+        <v>0101081010881010102030401015101010100</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Dang Nguyen48_2026-3-11.xlsx
+++ b/DateBase/orders/Dang Nguyen48_2026-3-11.xlsx
@@ -607,6 +607,9 @@
       <c r="C21" t="str">
         <v>791_菟葵黑_undefined_undefined_1bunch</v>
       </c>
+      <c r="F21" t="str">
+        <v>5</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
@@ -665,7 +668,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>0101081010881010102030401015101010100</v>
+        <v>0101081010881010102030401015101010105</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Dang Nguyen48_2026-3-11.xlsx
+++ b/DateBase/orders/Dang Nguyen48_2026-3-11.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L21"/>
+  <dimension ref="A1:L31"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -611,9 +611,86 @@
         <v>5</v>
       </c>
     </row>
+    <row r="22">
+      <c r="C22" t="str">
+        <v>329_柔丝_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F22" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="C23" t="str">
+        <v>528_五代果_pig face_undefined_1bunch</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="str">
+        <v>4</v>
+      </c>
+      <c r="C24" t="str">
+        <v>41_拉丝白_Spider White_Gerbera L._20stems</v>
+      </c>
+      <c r="F24" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="C25" t="str">
+        <v>77_珍爱mini_undefined_Gerbera L._20stems</v>
+      </c>
+      <c r="F25" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="C26" t="str">
+        <v>70_朝霞mini_undefined_Gerbera L._20stems</v>
+      </c>
+      <c r="F26" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="C27" t="str">
+        <v>42_拉丝黄_Spider Yellow_Gerbera L._20stems</v>
+      </c>
+      <c r="F27" t="str">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="C28" t="str">
+        <v>46_拉丝橙_Spider orange_Gerbera L._20stems</v>
+      </c>
+      <c r="F28" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="C29" t="str">
+        <v>631_吸色康乃馨宝蓝_tinted blue_undefined_20stems</v>
+      </c>
+      <c r="F29" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="C30" t="str">
+        <v>632_吸色康乃馨紫_tinted purple_undefined_20stems</v>
+      </c>
+      <c r="F30" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="C31" t="str">
+        <v>615_康乃馨野马_horse_undefined_20stems</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L21"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L31"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -668,7 +745,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>0101081010881010102030401015101010105</v>
+        <v>0101081010881010102030401015101010105100101010410550</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Dang Nguyen48_2026-3-11.xlsx
+++ b/DateBase/orders/Dang Nguyen48_2026-3-11.xlsx
@@ -687,6 +687,9 @@
       <c r="C31" t="str">
         <v>615_康乃馨野马_horse_undefined_20stems</v>
       </c>
+      <c r="F31" t="str">
+        <v>10</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
@@ -745,7 +748,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>0101081010881010102030401015101010105100101010410550</v>
+        <v>01010810108810101020304010151010101051001010104105510</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Dang Nguyen48_2026-3-11.xlsx
+++ b/DateBase/orders/Dang Nguyen48_2026-3-11.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L31"/>
+  <dimension ref="A1:L41"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -691,9 +691,105 @@
         <v>10</v>
       </c>
     </row>
+    <row r="32">
+      <c r="C32" t="str">
+        <v>612_康乃馨古巴爱情_cuba love_undefined_20stems</v>
+      </c>
+      <c r="F32" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="C33" t="str">
+        <v>605_康乃馨流光粉_light pink_undefined_20stems</v>
+      </c>
+      <c r="F33" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="C34" t="str">
+        <v>625_多丁紫蝴蝶_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F34" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="C35" t="str">
+        <v>626_多丁莫言_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F35" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="C36" t="str">
+        <v>624_多丁白_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F36" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="str">
+        <v>5</v>
+      </c>
+      <c r="C37" t="str">
+        <v>845_干花紫罗兰_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F37" t="str">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="38" xml:space="preserve">
+      <c r="A38" t="str">
+        <v>1</v>
+      </c>
+      <c r="C38" t="str" xml:space="preserve">
+        <v xml:space="preserve">373_龙柳_Salix
+_undefined_1bunch</v>
+      </c>
+      <c r="F38" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="39" xml:space="preserve">
+      <c r="A39" t="str">
+        <v>2</v>
+      </c>
+      <c r="C39" t="str" xml:space="preserve">
+        <v xml:space="preserve">373_龙柳_Salix
+_undefined_1bunch</v>
+      </c>
+      <c r="F39" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="40" xml:space="preserve">
+      <c r="A40" t="str">
+        <v>3</v>
+      </c>
+      <c r="C40" t="str" xml:space="preserve">
+        <v xml:space="preserve">373_龙柳_Salix
+_undefined_1bunch</v>
+      </c>
+      <c r="F40" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="41" xml:space="preserve">
+      <c r="A41" t="str">
+        <v>4</v>
+      </c>
+      <c r="C41" t="str" xml:space="preserve">
+        <v xml:space="preserve">373_龙柳_Salix
+_undefined_1bunch</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L31"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L41"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -748,7 +844,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>01010810108810101020304010151010101051001010104105510</v>
+        <v>01010810108810101020304010151010101051001010104105510510555305550</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Dang Nguyen48_2026-3-11.xlsx
+++ b/DateBase/orders/Dang Nguyen48_2026-3-11.xlsx
@@ -786,6 +786,9 @@
         <v xml:space="preserve">373_龙柳_Salix
 _undefined_1bunch</v>
       </c>
+      <c r="F41" t="str">
+        <v>5</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
@@ -844,7 +847,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>01010810108810101020304010151010101051001010104105510510555305550</v>
+        <v>01010810108810101020304010151010101051001010104105510510555305555</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Dang Nguyen48_2026-3-11.xlsx
+++ b/DateBase/orders/Dang Nguyen48_2026-3-11.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L41"/>
+  <dimension ref="A1:L51"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -790,9 +790,94 @@
         <v>5</v>
       </c>
     </row>
+    <row r="42">
+      <c r="A42" t="str">
+        <v>5</v>
+      </c>
+      <c r="C42" t="str">
+        <v>147_娜欧米_Red Naomi_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F42" t="str">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="C43" t="str">
+        <v>268_猩红泡泡_spray red_Rosa rugosa Thunb._10stems</v>
+      </c>
+      <c r="F43" t="str">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="C44" t="str">
+        <v>9_茶色洋桔梗_Tea Color Lisianthus_Eustoma grandiflorum (Raf.) Shinners_800/600g</v>
+      </c>
+      <c r="F44" t="str">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="C45" t="str">
+        <v>614_康乃馨绿_green_undefined_20stems</v>
+      </c>
+      <c r="F45" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="str">
+        <v>6</v>
+      </c>
+      <c r="C46" t="str">
+        <v>532_灯苔_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F46" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="C47" t="str">
+        <v>843_灯台_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F47" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="C48" t="str">
+        <v>462_五针松_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F48" t="str">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="C49" t="str">
+        <v>327_文竹_asparagus fern_undefined_1bunch</v>
+      </c>
+      <c r="F49" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="50" xml:space="preserve">
+      <c r="C50" t="str" xml:space="preserve">
+        <v xml:space="preserve">448_吊米 绿_hanging amaranthus
+green_undefined_1bunch</v>
+      </c>
+      <c r="F50" t="str">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="51" xml:space="preserve">
+      <c r="C51" t="str" xml:space="preserve">
+        <v xml:space="preserve">542_吊米 红_hanging amaranthus
+red_undefined_1bunch</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L41"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L51"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -847,7 +932,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>01010810108810101020304010151010101051001010104105510510555305555</v>
+        <v>010108101088101010203040101510101010510010101041055105105553055551620121055151080</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Dang Nguyen48_2026-3-11.xlsx
+++ b/DateBase/orders/Dang Nguyen48_2026-3-11.xlsx
@@ -874,6 +874,9 @@
         <v xml:space="preserve">542_吊米 红_hanging amaranthus
 red_undefined_1bunch</v>
       </c>
+      <c r="F51" t="str">
+        <v>10</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
@@ -932,7 +935,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>010108101088101010203040101510101010510010101041055105105553055551620121055151080</v>
+        <v>0101081010881010102030401015101010105100101010410551051055530555516201210551510810</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Dang Nguyen48_2026-3-11.xlsx
+++ b/DateBase/orders/Dang Nguyen48_2026-3-11.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L51"/>
+  <dimension ref="A1:L61"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -878,9 +878,89 @@
         <v>10</v>
       </c>
     </row>
+    <row r="52">
+      <c r="C52" t="str">
+        <v>328_卢荀草_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F52" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="C53" t="str">
+        <v>114_绣球孔雀蓝_Hydrangea Peacoke_Hydrangea L._1stem</v>
+      </c>
+      <c r="F53" t="str">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="C54" t="str">
+        <v>129_绣球初恋_Hydrangea Peacoke_Hydrangea L._1stem</v>
+      </c>
+      <c r="F54" t="str">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="C55" t="str">
+        <v>457_茴香花_lace flower yellow_undefined_1bunch</v>
+      </c>
+      <c r="F55" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="C56" t="str">
+        <v>479_绿灵草_lepidium_undefined_1bunch</v>
+      </c>
+      <c r="F56" t="str">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="str">
+        <v>7</v>
+      </c>
+      <c r="C57" t="str">
+        <v>651_大丽花 奶油桃子_undefined_undefined_5stems</v>
+      </c>
+      <c r="F57" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="C58" t="str">
+        <v>797_大菊黄_undefined_undefined_5stems</v>
+      </c>
+      <c r="F58" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="C59" t="str">
+        <v>791_菟葵黑_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F59" t="str">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="C60" t="str">
+        <v>528_五代果_pig face_undefined_1bunch</v>
+      </c>
+      <c r="F60" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="C61" t="str">
+        <v>643_巧克力秋英_undefined_undefined_1bunch</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L51"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L61"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -935,7 +1015,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>0101081010881010102030401015101010105100101010410551051055530555516201210551510810</v>
+        <v>010108101088101010203040101510101010510010101041055105105553055551620121055151081010172010301010350</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Dang Nguyen48_2026-3-11.xlsx
+++ b/DateBase/orders/Dang Nguyen48_2026-3-11.xlsx
@@ -957,6 +957,9 @@
       <c r="C61" t="str">
         <v>643_巧克力秋英_undefined_undefined_1bunch</v>
       </c>
+      <c r="F61" t="str">
+        <v>5</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
@@ -1015,7 +1018,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>010108101088101010203040101510101010510010101041055105105553055551620121055151081010172010301010350</v>
+        <v>010108101088101010203040101510101010510010101041055105105553055551620121055151081010172010301010355</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Dang Nguyen48_2026-3-11.xlsx
+++ b/DateBase/orders/Dang Nguyen48_2026-3-11.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L61"/>
+  <dimension ref="A1:L71"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -961,9 +961,89 @@
         <v>5</v>
       </c>
     </row>
+    <row r="62">
+      <c r="C62" t="str">
+        <v>589_洋牡丹香槟_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F62" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="C63" t="str">
+        <v>421_松虫草黑色_scabiosa black_undefined_1bunch</v>
+      </c>
+      <c r="F63" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="str">
+        <v>8</v>
+      </c>
+      <c r="C64" t="str">
+        <v>144_高原红_High Plateau Red_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F64" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="C65" t="str">
+        <v>152_白荔枝_White Ohara_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F65" t="str">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="C66" t="str">
+        <v>483_圣诞花_mimosa_undefined_1bunch</v>
+      </c>
+      <c r="F66" t="str">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="C67" t="str">
+        <v>586_洋牡丹白_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F67" t="str">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="C68" t="str">
+        <v>590_洋牡丹粉_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F68" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="C69" t="str">
+        <v>585_洋牡丹红_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F69" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="C70" t="str">
+        <v>591_洋牡丹黑_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F70" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="C71" t="str">
+        <v>588_洋牡丹黄_undefined_undefined_1bunch</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L61"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L71"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -1018,7 +1098,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>010108101088101010203040101510101010510010101041055105105553055551620121055151081010172010301010355</v>
+        <v>010108101088101010203040101510101010510010101041055105105553055551620121055151081010172010301010355551071515101050</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Dang Nguyen48_2026-3-11.xlsx
+++ b/DateBase/orders/Dang Nguyen48_2026-3-11.xlsx
@@ -1040,6 +1040,9 @@
       <c r="C71" t="str">
         <v>588_洋牡丹黄_undefined_undefined_1bunch</v>
       </c>
+      <c r="F71" t="str">
+        <v>5</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
@@ -1098,7 +1101,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>010108101088101010203040101510101010510010101041055105105553055551620121055151081010172010301010355551071515101050</v>
+        <v>010108101088101010203040101510101010510010101041055105105553055551620121055151081010172010301010355551071515101055</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Dang Nguyen48_2026-3-11.xlsx
+++ b/DateBase/orders/Dang Nguyen48_2026-3-11.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L71"/>
+  <dimension ref="A1:L74"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -993,7 +993,7 @@
         <v>152_白荔枝_White Ohara_Rosa rugosa Thunb._20stems</v>
       </c>
       <c r="F65" t="str">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="66">
@@ -1038,15 +1038,39 @@
     </row>
     <row r="71">
       <c r="C71" t="str">
+        <v>587_洋牡丹橙_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F71" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="C72" t="str">
         <v>588_洋牡丹黄_undefined_undefined_1bunch</v>
       </c>
-      <c r="F71" t="str">
+      <c r="F72" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="C73" t="str">
+        <v>820_蝴蝶洋牡丹粉_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F73" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="C74" t="str">
+        <v>480_蝴蝶洋牡丹红_butterfly  Ranunculus_undefined_1bunch</v>
+      </c>
+      <c r="F74" t="str">
         <v>5</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L71"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L74"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -1101,7 +1125,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>010108101088101010203040101510101010510010101041055105105553055551620121055151081010172010301010355551071515101055</v>
+        <v>010108101088101010203040101510101010510010101041055105105553055551620121055151081010172010301010355551061515101055555</v>
       </c>
     </row>
   </sheetData>
